--- a/storage/template/TEMPLATE-JADWAL-PATROLI.xlsx
+++ b/storage/template/TEMPLATE-JADWAL-PATROLI.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/imamsyz/Project/ASTRA/ASTRA_2023/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/imamsyz/PhpstormProjects/digipatrol.id/storage/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25BF5E9-0B62-EE46-812C-C161FFB2926E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536B099E-AA73-604A-801E-C18ECAB413BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JADWAL PATROLI" sheetId="7" r:id="rId1"/>
-    <sheet name="BULAN" sheetId="6" r:id="rId2"/>
+    <sheet name="SHIFT" sheetId="8" r:id="rId2"/>
+    <sheet name="BULAN" sheetId="6" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="33">
   <si>
     <t>PT. ABC</t>
   </si>
@@ -97,12 +98,51 @@
   </si>
   <si>
     <t xml:space="preserve"> Perusahaan</t>
+  </si>
+  <si>
+    <t>Shift Name</t>
+  </si>
+  <si>
+    <t>Shift Code</t>
+  </si>
+  <si>
+    <t>Start Hour</t>
+  </si>
+  <si>
+    <t>End Hour</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>SHIFT 3</t>
+  </si>
+  <si>
+    <t>SHIFT 2</t>
+  </si>
+  <si>
+    <t>SHIFT 1</t>
+  </si>
+  <si>
+    <t>SH-1</t>
+  </si>
+  <si>
+    <t>SH-2</t>
+  </si>
+  <si>
+    <t>SH-3</t>
+  </si>
+  <si>
+    <t>LB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="hh\:mm"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -134,7 +174,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -142,44 +182,97 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -231,14 +324,14 @@
   </dxfs>
   <tableStyles count="2">
     <tableStyle name="SAMPLE KATEGORI-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="secondRowStripe" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="secondRowStripe" dxfId="7"/>
     </tableStyle>
     <tableStyle name="KATEGORI-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -450,609 +543,582 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE28329-74F9-E246-A43B-03441B3463AD}">
-  <dimension ref="A2:L38"/>
+  <dimension ref="A2:F37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A3" s="2" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="4">
+      <c r="B4" s="10"/>
+      <c r="C4" s="12">
         <v>2023</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="D4" s="12"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="8"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="9"/>
-      <c r="B6" s="11">
+      <c r="B6" s="4">
         <v>1111</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="4">
         <v>2222</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="4">
         <v>3333</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="4">
         <v>4444</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A7" s="5">
         <v>1</v>
       </c>
-      <c r="B7" s="1">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1">
+      <c r="B7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A8" s="5">
         <v>2</v>
       </c>
-      <c r="D7" s="1">
-        <v>3</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" s="1">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A10">
+      <c r="B8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A9" s="5">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A10" s="5">
         <v>4</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A11">
+      <c r="B10" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A11" s="5">
         <v>5</v>
       </c>
-      <c r="B11" s="1">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2</v>
-      </c>
-      <c r="D11" s="1">
-        <v>3</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A12">
+      <c r="B11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A12" s="5">
         <v>6</v>
       </c>
-      <c r="B12" s="1">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1">
-        <v>3</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A13">
+      <c r="B12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A13" s="5">
         <v>7</v>
       </c>
-      <c r="B13" s="1">
-        <v>3</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A14">
+      <c r="B13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A14" s="5">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1</v>
-      </c>
-      <c r="D14" s="1">
-        <v>2</v>
-      </c>
-      <c r="E14" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A15">
+      <c r="B14" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A15" s="5">
         <v>9</v>
       </c>
-      <c r="B15" s="1">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1">
-        <v>2</v>
-      </c>
-      <c r="D15" s="1">
-        <v>3</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A16">
+      <c r="B15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A16" s="5">
         <v>10</v>
       </c>
-      <c r="B16" s="1">
-        <v>2</v>
-      </c>
-      <c r="C16" s="1">
-        <v>3</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
+      <c r="B16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17">
+      <c r="A17" s="5">
         <v>11</v>
       </c>
-      <c r="B17" s="1">
-        <v>3</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1">
-        <v>2</v>
+      <c r="B17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18">
+      <c r="A18" s="5">
         <v>12</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
-      <c r="E18" s="1">
-        <v>3</v>
+      <c r="B18" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19">
+      <c r="A19" s="5">
         <v>13</v>
       </c>
-      <c r="B19" s="1">
-        <v>1</v>
-      </c>
-      <c r="C19" s="1">
-        <v>2</v>
-      </c>
-      <c r="D19" s="1">
-        <v>3</v>
-      </c>
-      <c r="E19" s="8" t="s">
+      <c r="B19" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20">
+      <c r="A20" s="5">
         <v>14</v>
       </c>
-      <c r="B20" s="1">
-        <v>2</v>
-      </c>
-      <c r="C20" s="1">
-        <v>3</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
+      <c r="B20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21">
+      <c r="A21" s="5">
         <v>15</v>
       </c>
-      <c r="B21" s="1">
-        <v>3</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1">
-        <v>2</v>
+      <c r="B21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22">
+      <c r="A22" s="5">
         <v>16</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1</v>
-      </c>
-      <c r="D22" s="1">
-        <v>2</v>
-      </c>
-      <c r="E22" s="1">
-        <v>3</v>
+      <c r="B22" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23">
+      <c r="A23" s="5">
         <v>17</v>
       </c>
-      <c r="B23" s="1">
-        <v>1</v>
-      </c>
-      <c r="C23" s="1">
-        <v>2</v>
-      </c>
-      <c r="D23" s="1">
-        <v>3</v>
-      </c>
-      <c r="E23" s="8" t="s">
+      <c r="B23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24">
+      <c r="A24" s="5">
         <v>18</v>
       </c>
-      <c r="B24" s="1">
-        <v>2</v>
-      </c>
-      <c r="C24" s="1">
-        <v>3</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="1">
-        <v>1</v>
+      <c r="B24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25">
+      <c r="A25" s="5">
         <v>19</v>
       </c>
-      <c r="B25" s="1">
-        <v>3</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1">
-        <v>2</v>
+      <c r="B25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26">
+      <c r="A26" s="5">
         <v>20</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="1">
-        <v>1</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2</v>
-      </c>
-      <c r="E26" s="1">
-        <v>3</v>
+      <c r="B26" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27">
+      <c r="A27" s="5">
         <v>21</v>
       </c>
-      <c r="B27" s="1">
-        <v>1</v>
-      </c>
-      <c r="C27" s="1">
-        <v>2</v>
-      </c>
-      <c r="D27" s="1">
-        <v>3</v>
-      </c>
-      <c r="E27" s="8" t="s">
+      <c r="B27" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28">
+      <c r="A28" s="5">
         <v>22</v>
       </c>
-      <c r="B28" s="1">
-        <v>2</v>
-      </c>
-      <c r="C28" s="1">
-        <v>3</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1</v>
+      <c r="B28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A29">
+      <c r="A29" s="5">
         <v>23</v>
       </c>
-      <c r="B29" s="1">
-        <v>3</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1">
-        <v>2</v>
+      <c r="B29" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A30">
+      <c r="A30" s="5">
         <v>24</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" s="1">
-        <v>1</v>
-      </c>
-      <c r="D30" s="1">
-        <v>2</v>
-      </c>
-      <c r="E30" s="1">
-        <v>3</v>
+      <c r="B30" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A31">
+      <c r="A31" s="5">
         <v>25</v>
       </c>
-      <c r="B31" s="1">
-        <v>1</v>
-      </c>
-      <c r="C31" s="1">
-        <v>2</v>
-      </c>
-      <c r="D31" s="1">
-        <v>3</v>
-      </c>
-      <c r="E31" s="8" t="s">
+      <c r="B31" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A32">
-        <v>26</v>
-      </c>
-      <c r="B32" s="1">
-        <v>2</v>
-      </c>
-      <c r="C32" s="1">
-        <v>3</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1</v>
+      <c r="A32" s="5">
+        <v>26</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A33">
-        <v>27</v>
-      </c>
-      <c r="B33" s="1">
-        <v>3</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1">
-        <v>2</v>
+      <c r="A33" s="5">
+        <v>27</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A34">
-        <v>28</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="1">
-        <v>1</v>
-      </c>
-      <c r="D34" s="1">
-        <v>2</v>
-      </c>
-      <c r="E34" s="1">
-        <v>3</v>
+      <c r="A34" s="5">
+        <v>28</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A35">
+      <c r="A35" s="5">
         <v>29</v>
       </c>
-      <c r="B35" s="1">
-        <v>1</v>
-      </c>
-      <c r="C35" s="1">
-        <v>2</v>
-      </c>
-      <c r="D35" s="1">
-        <v>3</v>
-      </c>
-      <c r="E35" s="8" t="s">
+      <c r="B35" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A36">
+      <c r="A36" s="5">
         <v>30</v>
       </c>
-      <c r="B36" s="1">
-        <v>2</v>
-      </c>
-      <c r="C36" s="1">
-        <v>3</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E36" s="1">
-        <v>1</v>
+      <c r="B36" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="C37" s="5"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B38" s="5"/>
+      <c r="B37" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1064,21 +1130,41 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
+  <conditionalFormatting sqref="B7:E36">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"SHIFT 2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" stopIfTrue="1" operator="equal">
+      <formula>"SHIFT 3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" stopIfTrue="1" operator="equal">
+      <formula>"SHIFT 1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+      <formula>"LIBUR"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{946A24F4-F36E-6844-86C1-86981797E137}">
           <x14:formula1>
             <xm:f>BULAN!$B$4:$B$11</xm:f>
           </x14:formula1>
-          <xm:sqref>C4 E4:L4</xm:sqref>
+          <xm:sqref>C4 E4:K4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D9F50F0E-372F-3A45-94B9-4C2CBF669EEE}">
           <x14:formula1>
             <xm:f>BULAN!$A$4:$A$15</xm:f>
           </x14:formula1>
-          <xm:sqref>C3 F3:L3</xm:sqref>
+          <xm:sqref>C3 F3:H3 J3:L3</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{167FC4DD-F93C-4444-96F3-052CEC1D2312}">
+          <x14:formula1>
+            <xm:f>SHIFT!$B$3:$B$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>B7:E36</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1087,6 +1173,104 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5427011B-65AD-4146-A0F9-4E95C526E51D}">
+  <dimension ref="A2:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0.29236111111111113</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0.62569444444444444</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.91736111111111107</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.29166666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.29236111111111113</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.29166666666666669</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7B8649-8753-2F41-9C37-96686A292ECD}">
   <dimension ref="A3:B15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -1095,15 +1279,15 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4">
@@ -1111,7 +1295,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5">
@@ -1119,7 +1303,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B6">
@@ -1127,7 +1311,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7">
@@ -1135,7 +1319,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B8">
@@ -1143,7 +1327,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B9">
@@ -1151,7 +1335,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B10">
@@ -1159,7 +1343,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B11">
@@ -1167,22 +1351,22 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
     </row>

--- a/storage/template/TEMPLATE-JADWAL-PATROLI.xlsx
+++ b/storage/template/TEMPLATE-JADWAL-PATROLI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/imamsyz/PhpstormProjects/digipatrol.id/storage/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536B099E-AA73-604A-801E-C18ECAB413BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C95726-3EAE-FD40-838B-C2023E050475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="2680" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JADWAL PATROLI" sheetId="7" r:id="rId1"/>

--- a/storage/template/TEMPLATE-JADWAL-PATROLI.xlsx
+++ b/storage/template/TEMPLATE-JADWAL-PATROLI.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/imamsyz/PhpstormProjects/digipatrol.id/storage/template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODE.ID\Muhammad Rizki Gajah\DigitalPatrol\digipatrol-backend\storage\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C95726-3EAE-FD40-838B-C2023E050475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="2680" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="2685" windowWidth="30240" windowHeight="18885" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="JADWAL PATROLI" sheetId="7" r:id="rId1"/>
@@ -139,7 +138,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="hh\:mm"/>
   </numFmts>
@@ -323,12 +322,12 @@
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle name="SAMPLE KATEGORI-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="SAMPLE KATEGORI-style" pivot="0" count="3">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="secondRowStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="KATEGORI-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="KATEGORI-style" pivot="0" count="3">
       <tableStyleElement type="headerRow" dxfId="6"/>
       <tableStyleElement type="firstRowStripe" dxfId="5"/>
       <tableStyleElement type="secondRowStripe" dxfId="4"/>
@@ -542,15 +541,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE28329-74F9-E246-A43B-03441B3463AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:F37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>20</v>
       </c>
@@ -559,7 +558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
@@ -570,7 +569,7 @@
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
@@ -580,7 +579,7 @@
       </c>
       <c r="D4" s="12"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>18</v>
       </c>
@@ -592,7 +591,7 @@
       <c r="E5" s="8"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="4">
         <v>1111</v>
@@ -607,7 +606,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>1</v>
       </c>
@@ -624,7 +623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>2</v>
       </c>
@@ -641,7 +640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>3</v>
       </c>
@@ -658,7 +657,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>4</v>
       </c>
@@ -675,7 +674,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>5</v>
       </c>
@@ -692,7 +691,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>6</v>
       </c>
@@ -709,7 +708,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>7</v>
       </c>
@@ -726,7 +725,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>8</v>
       </c>
@@ -743,7 +742,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>9</v>
       </c>
@@ -760,7 +759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>10</v>
       </c>
@@ -777,7 +776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>11</v>
       </c>
@@ -794,7 +793,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>12</v>
       </c>
@@ -811,7 +810,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>13</v>
       </c>
@@ -828,7 +827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>14</v>
       </c>
@@ -845,7 +844,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>15</v>
       </c>
@@ -862,7 +861,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>16</v>
       </c>
@@ -879,7 +878,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>17</v>
       </c>
@@ -896,7 +895,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>18</v>
       </c>
@@ -913,7 +912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>19</v>
       </c>
@@ -930,7 +929,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>20</v>
       </c>
@@ -947,7 +946,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>21</v>
       </c>
@@ -964,7 +963,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>22</v>
       </c>
@@ -981,7 +980,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>23</v>
       </c>
@@ -998,7 +997,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>24</v>
       </c>
@@ -1015,7 +1014,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>25</v>
       </c>
@@ -1032,7 +1031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>26</v>
       </c>
@@ -1049,7 +1048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <v>27</v>
       </c>
@@ -1066,7 +1065,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <v>28</v>
       </c>
@@ -1083,7 +1082,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>29</v>
       </c>
@@ -1100,7 +1099,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>30</v>
       </c>
@@ -1117,7 +1116,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B37" s="1"/>
     </row>
   </sheetData>
@@ -1148,19 +1147,19 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{946A24F4-F36E-6844-86C1-86981797E137}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>BULAN!$B$4:$B$11</xm:f>
           </x14:formula1>
           <xm:sqref>C4 E4:K4</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D9F50F0E-372F-3A45-94B9-4C2CBF669EEE}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>BULAN!$A$4:$A$15</xm:f>
           </x14:formula1>
           <xm:sqref>C3 F3:H3 J3:L3</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{167FC4DD-F93C-4444-96F3-052CEC1D2312}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>SHIFT!$B$3:$B$6</xm:f>
           </x14:formula1>
@@ -1173,14 +1172,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5427011B-65AD-4146-A0F9-4E95C526E51D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>25</v>
       </c>
@@ -1197,7 +1196,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -1214,7 +1213,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -1231,7 +1230,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -1248,7 +1247,7 @@
         <v>0.29166666666666669</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -1271,14 +1270,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7B8649-8753-2F41-9C37-96686A292ECD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1286,7 +1285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1294,7 +1293,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1302,7 +1301,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1310,7 +1309,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -1318,7 +1317,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -1326,7 +1325,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1334,7 +1333,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1342,7 +1341,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1350,22 +1349,22 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
